--- a/approaches/examples/disposable-medical-gloves/2B_market.xlsx
+++ b/approaches/examples/disposable-medical-gloves/2B_market.xlsx
@@ -9,11 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Application (bottom-up)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Material" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Product Form" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Sterility" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Distribution Channel" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method &amp; Evidence" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Type" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Form" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method &amp; Evidence" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -533,7 +531,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4902966.1999</v>
+        <v>31342.5614</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>1</v>
@@ -551,10 +549,10 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>742890.5899</v>
+        <v>2129.2597</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>0.1515186031498956</v>
+        <v>0.06793508905752675</v>
       </c>
     </row>
     <row r="8">
@@ -569,10 +567,10 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>643491.4575</v>
+        <v>1963.5597</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.1312453382838178</v>
+        <v>0.0626483481978598</v>
       </c>
     </row>
     <row r="9">
@@ -587,10 +585,10 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>99399.1324</v>
+        <v>165.7</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0.02027326486607787</v>
+        <v>0.005286740859666944</v>
       </c>
     </row>
     <row r="10">
@@ -605,10 +603,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>212443.7167</v>
+        <v>403.2366</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>0.04332963109236464</v>
+        <v>0.01286546414805779</v>
       </c>
     </row>
     <row r="11">
@@ -623,10 +621,10 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>60820.7134</v>
+        <v>269.1866</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>0.01240488123316871</v>
+        <v>0.008588532269733386</v>
       </c>
     </row>
     <row r="12">
@@ -641,10 +639,10 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>151623.0033</v>
+        <v>134.05</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.03092474985919594</v>
+        <v>0.004276931878324406</v>
       </c>
     </row>
     <row r="13">
@@ -659,10 +657,10 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>780375.4795</v>
+        <v>1613.902</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>0.1591639525305959</v>
+        <v>0.05149234548520339</v>
       </c>
     </row>
     <row r="14">
@@ -677,10 +675,10 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>237753.8695</v>
+        <v>555.26</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0.04849184346913286</v>
+        <v>0.017715846286896</v>
       </c>
     </row>
     <row r="15">
@@ -695,10 +693,10 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>202884.884</v>
+        <v>452.2</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.04138002909425278</v>
+        <v>0.01442766576186718</v>
       </c>
     </row>
     <row r="16">
@@ -713,10 +711,10 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>176603.69</v>
+        <v>185.842</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.03601976493405196</v>
+        <v>0.005929381381063515</v>
       </c>
     </row>
     <row r="17">
@@ -731,10 +729,10 @@
         </is>
       </c>
       <c r="C17" s="9" t="n">
-        <v>163133.036</v>
+        <v>420.6</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.03327231503315834</v>
+        <v>0.01341945205537669</v>
       </c>
     </row>
     <row r="18">
@@ -749,10 +747,10 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>1956947.6138</v>
+        <v>25272.1631</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>0.3991354486269788</v>
+        <v>0.8063209250026389</v>
       </c>
     </row>
     <row r="19">
@@ -767,10 +765,10 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>994552.64</v>
+        <v>23069.9807</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.2028471336433616</v>
+        <v>0.736059200956052</v>
       </c>
     </row>
     <row r="20">
@@ -785,10 +783,10 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>351875.02</v>
+        <v>700.5</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.07176778416444657</v>
+        <v>0.02234980067710739</v>
       </c>
     </row>
     <row r="21">
@@ -803,10 +801,10 @@
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>410984.6</v>
+        <v>1200</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.08382366576550788</v>
+        <v>0.03828659644900624</v>
       </c>
     </row>
     <row r="22">
@@ -821,64 +819,46 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>121087.6271</v>
+        <v>301.6824</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.02469681049452669</v>
+        <v>0.009625326920473066</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Australia</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Rest of World</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>1924</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>0.06138617630657334</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Rest of World</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n">
-        <v>78447.7267</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>0.01600005455913606</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Rest of World</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="n">
-        <v>1210308.8</v>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>0.2468523646001649</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Rest of World</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="n">
-        <v>1210308.8</v>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>0.2468523646001649</v>
+      <c r="C24" s="9" t="n">
+        <v>1924</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>0.06138617630657334</v>
       </c>
     </row>
   </sheetData>
@@ -892,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -928,7 +908,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Surgical/Operating Room</t>
+          <t>Surgical Procedures</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -938,27 +918,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Chemotherapy &amp; Hazardous Drug Handling</t>
+          <t>Diagnostic &amp; Pathology Laboratories</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Infection Control &amp; Environmental Cleaning</t>
+          <t>Dental &amp; Oral Care</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Diagnostic &amp; Laboratory Procedures</t>
+          <t>Emergency, EMS &amp; First Response</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Emergency &amp; First Response</t>
+          <t>Home Healthcare &amp; Non-Acute Clinical Care</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Dental &amp; Outpatient Specialty Care</t>
+          <t>Pharmacy &amp; Clinical Compounding</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -974,28 +954,28 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>699.9001</v>
+        <v>21022.755</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>241666.25</v>
+        <v>4868.112</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>40.3884</v>
+        <v>387.9</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1089.6</v>
+        <v>1292.5144</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>8646.040000000001</v>
+        <v>515.88</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>94363.7062</v>
+        <v>3051</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>4556460.3152</v>
+        <v>204.4</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>4902966.1999</v>
+        <v>31342.5614</v>
       </c>
     </row>
     <row r="5">
@@ -1005,28 +985,28 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>162.01</v>
+        <v>89.25</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>15625</v>
+        <v>312</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>5.7924</v>
+        <v>81</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>312</v>
+        <v>176.9797</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>2920</v>
+        <v>54.18</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>20865.7875</v>
+        <v>1361.25</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>703000</v>
+        <v>54.6</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>742890.5899</v>
+        <v>2129.2597</v>
       </c>
     </row>
     <row r="6">
@@ -1036,28 +1016,28 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>156.91</v>
+        <v>85</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>12500</v>
+        <v>240</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>5.76</v>
+        <v>75</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>288</v>
+        <v>162.5797</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>2800</v>
+        <v>46.98</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>19740.7875</v>
+        <v>1305</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>608000</v>
+        <v>49</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>643491.4575</v>
+        <v>1963.5597</v>
       </c>
     </row>
     <row r="7">
@@ -1067,28 +1047,28 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>5.1</v>
+        <v>4.25</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3125</v>
+        <v>72</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0324</v>
+        <v>6</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>24</v>
+        <v>14.4</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>120</v>
+        <v>7.2</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>1125</v>
+        <v>56.25</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>95000</v>
+        <v>5.6</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>99399.1324</v>
+        <v>165.7</v>
       </c>
     </row>
     <row r="8">
@@ -1098,28 +1078,28 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>44.8366</v>
+        <v>45.6866</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>7500</v>
+        <v>144</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>1.728</v>
+        <v>12</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>55.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>300</v>
+        <v>2.7</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0</v>
+        <v>101.25</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>204541.9521</v>
+        <v>11.2</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>212443.7167</v>
+        <v>403.2366</v>
       </c>
     </row>
     <row r="9">
@@ -1132,25 +1112,25 @@
         <v>37.1866</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>5000</v>
+        <v>96</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1.08</v>
+        <v>7.5</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>55546.4468</v>
+        <v>7</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>60820.7134</v>
+        <v>269.1866</v>
       </c>
     </row>
     <row r="10">
@@ -1160,28 +1140,28 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>7.65</v>
+        <v>8.5</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>2500</v>
+        <v>48</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.648</v>
+        <v>4.5</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>19.2</v>
+        <v>32.4</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>100</v>
+        <v>2.7</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0</v>
+        <v>33.75</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>148995.5053</v>
+        <v>4.2</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>151623.0033</v>
+        <v>134.05</v>
       </c>
     </row>
     <row r="11">
@@ -1191,28 +1171,28 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>65.84350000000001</v>
+        <v>84.66</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>24166.25</v>
+        <v>440.112</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>6.336</v>
+        <v>54.9</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>180</v>
+        <v>335.88</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>800.8</v>
+        <v>104.4</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>14156.25</v>
+        <v>551.25</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>741000</v>
+        <v>42.7</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>780375.4795</v>
+        <v>1613.902</v>
       </c>
     </row>
     <row r="12">
@@ -1222,28 +1202,28 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>28.1035</v>
+        <v>30.26</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>8125</v>
+        <v>168</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>2.016</v>
+        <v>15</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>60</v>
+        <v>136.8</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>320</v>
+        <v>12.6</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>1218.75</v>
+        <v>180</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>228000</v>
+        <v>12.6</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>237753.8695</v>
+        <v>555.26</v>
       </c>
     </row>
     <row r="13">
@@ -1253,28 +1233,28 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>15.3</v>
+        <v>20.4</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>6875</v>
+        <v>144</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1.584</v>
+        <v>12</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>320</v>
+        <v>21.6</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>5625</v>
+        <v>135</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>190000</v>
+        <v>11.2</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>202884.884</v>
+        <v>452.2</v>
       </c>
     </row>
     <row r="14">
@@ -1287,25 +1267,25 @@
         <v>17</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>4791.25</v>
+        <v>8.112</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>1.44</v>
+        <v>18.9</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>43.2</v>
+        <v>1.08</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>0.8</v>
+        <v>7.2</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>750</v>
+        <v>123.75</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>171000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>176603.69</v>
+        <v>185.842</v>
       </c>
     </row>
     <row r="15">
@@ -1315,28 +1295,28 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>5.44</v>
+        <v>17</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>4375</v>
+        <v>120</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>1.296</v>
+        <v>9</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>28.8</v>
+        <v>90</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>6562.5</v>
+        <v>112.5</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>152000</v>
+        <v>9.1</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>163133.036</v>
+        <v>420.6</v>
       </c>
     </row>
     <row r="16">
@@ -1346,28 +1326,28 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>223.21</v>
+        <v>20599.1584</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>163125</v>
+        <v>2772</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>15.732</v>
+        <v>180</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>398.4</v>
+        <v>261.2547</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>3425.24</v>
+        <v>354.6</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>21841.6687</v>
+        <v>1037.25</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>1767918.3631</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1956947.6138</v>
+        <v>25272.1631</v>
       </c>
     </row>
     <row r="17">
@@ -1377,28 +1357,28 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>102</v>
+        <v>20400</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>133125</v>
+        <v>1800</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>8.640000000000001</v>
+        <v>105</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>192</v>
+        <v>23.4807</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>2000</v>
+        <v>144</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>4125</v>
+        <v>562.5</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>855000</v>
+        <v>35</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>994552.64</v>
+        <v>23069.9807</v>
       </c>
     </row>
     <row r="18">
@@ -1411,25 +1391,25 @@
         <v>25.5</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>9375</v>
+        <v>192</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>72</v>
+        <v>151.2</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>400</v>
+        <v>45</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>342000</v>
+        <v>16.8</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>351875.02</v>
+        <v>700.5</v>
       </c>
     </row>
     <row r="19">
@@ -1439,28 +1419,28 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>15000</v>
+        <v>720</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>3.6</v>
+        <v>45</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>96</v>
+        <v>64.8</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>800</v>
+        <v>144</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>15000</v>
+        <v>45</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>380000</v>
+        <v>11.2</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>410984.6</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="20">
@@ -1470,121 +1450,90 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>6.8</v>
+        <v>3.6584</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>3750</v>
+        <v>60</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.864</v>
+        <v>30</v>
       </c>
       <c r="E20" s="9" t="n">
+        <v>21.774</v>
+      </c>
+      <c r="F20" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="F20" s="9" t="n">
-        <v>140</v>
-      </c>
       <c r="G20" s="9" t="n">
-        <v>2250</v>
+        <v>159.75</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>114918.3631</v>
+        <v>4.9</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>121087.6271</v>
+        <v>301.6824</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Australia</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>1875</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>85.23999999999999</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>466.6687</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>76000</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>78447.7267</v>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Rest of World</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>204</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>432</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>1924</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Rest of World</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Rest of World</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
         <v>204</v>
       </c>
-      <c r="C22" s="7" t="n">
-        <v>31250</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>144</v>
-      </c>
-      <c r="F22" s="7" t="n">
+      <c r="C22" s="9" t="n">
         <v>1200</v>
       </c>
-      <c r="G22" s="7" t="n">
-        <v>37500</v>
-      </c>
-      <c r="H22" s="7" t="n">
-        <v>1140000</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>1210308.8</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Rest of World</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n">
-        <v>204</v>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>31250</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>144</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>1200</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>37500</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>1140000</v>
-      </c>
-      <c r="I23" s="9" t="n">
-        <v>1210308.8</v>
+      <c r="D22" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>432</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="I22" s="9" t="n">
+        <v>1924</v>
       </c>
     </row>
   </sheetData>
@@ -1598,7 +1547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1614,7 +1563,7 @@
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>By Material -- TOP-DOWN (country total x share)</t>
+          <t>By Type -- TOP-DOWN (country total x share)</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1582,32 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Nitrile</t>
+          <t>Natural Rubber Gloves</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Latex</t>
+          <t>Nitrile Gloves</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Vinyl</t>
+          <t>Vinyl Gloves</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Neoprene</t>
+          <t>Neoprene Gloves</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Polyethylene</t>
+          <t>Polyethylene Gloves</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Other Materials</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1674,25 +1623,25 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2237691.6904</v>
+        <v>8872.218800000001</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1348532.8529</v>
+        <v>13246.4075</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>801171.3101</v>
+        <v>5358.3957</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>170213.2892</v>
+        <v>740.9981</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>247297.7333</v>
+        <v>2497.6902</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>98059.32399999999</v>
+        <v>626.8511</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>4902966.1999</v>
+        <v>31342.5614</v>
       </c>
     </row>
     <row r="5">
@@ -1702,25 +1651,25 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>407595.8331</v>
+        <v>475.0651</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>164429.9211</v>
+        <v>1103.901</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>95581.78539999999</v>
+        <v>255.5112</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>29715.6236</v>
+        <v>85.1704</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>30709.6149</v>
+        <v>167.0268</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>14857.8118</v>
+        <v>42.5852</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>742890.5899</v>
+        <v>2129.2597</v>
       </c>
     </row>
     <row r="6">
@@ -1730,25 +1679,25 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>353920.3016</v>
+        <v>431.9831</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>141568.1206</v>
+        <v>1021.051</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>83653.8895</v>
+        <v>235.6272</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>25739.6583</v>
+        <v>78.5424</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>25739.6583</v>
+        <v>157.0848</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>12869.8292</v>
+        <v>39.2712</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>643491.4575</v>
+        <v>1963.5597</v>
       </c>
     </row>
     <row r="7">
@@ -1758,25 +1707,25 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>53675.5315</v>
+        <v>43.082</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>22861.8005</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>11927.8959</v>
+        <v>19.884</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>3975.9653</v>
+        <v>6.628</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>4969.9566</v>
+        <v>9.942</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>1987.9826</v>
+        <v>3.314</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>99399.1324</v>
+        <v>165.7</v>
       </c>
     </row>
     <row r="8">
@@ -1786,25 +1735,25 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>94991.4654</v>
+        <v>137.1222</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>60700.6549</v>
+        <v>150.5272</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>35507.2247</v>
+        <v>64.5179</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>6373.3115</v>
+        <v>8.0647</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>10622.1859</v>
+        <v>34.9399</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>4248.8743</v>
+        <v>8.0647</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>212443.7167</v>
+        <v>403.2366</v>
       </c>
     </row>
     <row r="9">
@@ -1814,25 +1763,25 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>26761.1139</v>
+        <v>96.9072</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>18246.214</v>
+        <v>96.9072</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>9731.3141</v>
+        <v>43.0699</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>1824.6214</v>
+        <v>5.3837</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>3041.0357</v>
+        <v>21.5349</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>1216.4143</v>
+        <v>5.3837</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>60820.7134</v>
+        <v>269.1866</v>
       </c>
     </row>
     <row r="10">
@@ -1842,25 +1791,25 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>68230.3515</v>
+        <v>40.215</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>42454.4409</v>
+        <v>53.62</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>25775.9106</v>
+        <v>21.448</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>4548.6901</v>
+        <v>2.681</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>7581.1502</v>
+        <v>13.405</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>3032.46</v>
+        <v>2.681</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>151623.0033</v>
+        <v>134.05</v>
       </c>
     </row>
     <row r="11">
@@ -1870,25 +1819,25 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>398609.5974</v>
+        <v>502.1158</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>194475.7669</v>
+        <v>724.4498</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>99071.2736</v>
+        <v>193.6682</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>33592.5579</v>
+        <v>64.5561</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>39018.774</v>
+        <v>96.83410000000001</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>15607.5097</v>
+        <v>32.278</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>780375.4795</v>
+        <v>1613.902</v>
       </c>
     </row>
     <row r="12">
@@ -1898,25 +1847,25 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>123632.0121</v>
+        <v>166.578</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>57060.9287</v>
+        <v>255.4196</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>28530.4643</v>
+        <v>66.63120000000001</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>11887.6935</v>
+        <v>22.2104</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>11887.6935</v>
+        <v>33.3156</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>4755.0774</v>
+        <v>11.1052</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>237753.8695</v>
+        <v>555.26</v>
       </c>
     </row>
     <row r="13">
@@ -1926,25 +1875,25 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>101442.442</v>
+        <v>144.704</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>52750.0698</v>
+        <v>198.968</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>26375.0349</v>
+        <v>54.264</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>8115.3954</v>
+        <v>18.088</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>10144.2442</v>
+        <v>27.132</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>4057.6977</v>
+        <v>9.044</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>202884.884</v>
+        <v>452.2</v>
       </c>
     </row>
     <row r="14">
@@ -1954,25 +1903,25 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>93599.95570000001</v>
+        <v>52.0358</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>40618.8487</v>
+        <v>89.2042</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>22958.4797</v>
+        <v>22.301</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>7064.1476</v>
+        <v>7.4337</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>8830.184499999999</v>
+        <v>11.1505</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>3532.0738</v>
+        <v>3.7168</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>176603.69</v>
+        <v>185.842</v>
       </c>
     </row>
     <row r="15">
@@ -1982,25 +1931,25 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>79935.1876</v>
+        <v>138.798</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>44045.9197</v>
+        <v>180.858</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>21207.2947</v>
+        <v>50.472</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>6525.3214</v>
+        <v>16.824</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>8156.6518</v>
+        <v>25.236</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>3262.6608</v>
+        <v>8.412000000000001</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>163133.036</v>
+        <v>420.6</v>
       </c>
     </row>
     <row r="16">
@@ -2010,25 +1959,25 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>852371.2745000001</v>
+        <v>7142.2357</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>565833.87</v>
+        <v>10536.4095</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>341052.3544</v>
+        <v>4536.8584</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>64222.5322</v>
+        <v>525.4869</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>94328.6305</v>
+        <v>2025.7294</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>39138.9522</v>
+        <v>505.4432</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>1956947.6138</v>
+        <v>25272.1631</v>
       </c>
     </row>
     <row r="17">
@@ -2038,25 +1987,25 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>417712.1088</v>
+        <v>6459.5946</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>278474.7392</v>
+        <v>9689.391900000001</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>198910.528</v>
+        <v>4152.5965</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>29836.5792</v>
+        <v>461.3996</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>49727.632</v>
+        <v>1845.5985</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>19891.0528</v>
+        <v>461.3996</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>994552.64</v>
+        <v>23069.9807</v>
       </c>
     </row>
     <row r="18">
@@ -2066,25 +2015,25 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>175937.51</v>
+        <v>238.17</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>98525.0056</v>
+        <v>294.21</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>42225.0024</v>
+        <v>84.06</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>14075.0008</v>
+        <v>28.02</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>14075.0008</v>
+        <v>42.03</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>7037.5004</v>
+        <v>14.01</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>351875.02</v>
+        <v>700.5</v>
       </c>
     </row>
     <row r="19">
@@ -2094,25 +2043,25 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>156174.148</v>
+        <v>360</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>139734.764</v>
+        <v>408</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>73977.228</v>
+        <v>264</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>12329.538</v>
+        <v>24</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>20549.23</v>
+        <v>120</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>8219.691999999999</v>
+        <v>24</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>410984.6</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="20">
@@ -2122,175 +2071,172 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>61754.6898</v>
+        <v>84.47110000000001</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>30271.9068</v>
+        <v>144.8076</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>15741.3915</v>
+        <v>36.2019</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>4843.5051</v>
+        <v>12.0673</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>6054.3814</v>
+        <v>18.1009</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>2421.7525</v>
+        <v>6.0336</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>121087.6271</v>
+        <v>301.6824</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Australia</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n">
-        <v>40792.8179</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>18827.4544</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>10198.2045</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>3137.9091</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>3922.3863</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>1568.9545</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>78447.7267</v>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Rest of World</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>615.6799999999999</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>731.12</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>307.84</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>57.72</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>173.16</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>38.48</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>1924</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Rest of World</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>484123.52</v>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>363092.64</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>229958.672</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>36309.264</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>72618.52800000001</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>24206.176</v>
-      </c>
-      <c r="H22" s="7" t="n">
-        <v>1210308.8</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t xml:space="preserve">   Rest of World</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n">
-        <v>484123.52</v>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>363092.64</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>229958.672</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>36309.264</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>72618.52800000001</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>24206.176</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>1210308.8</v>
+      <c r="B22" s="9" t="n">
+        <v>615.6799999999999</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>731.12</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>307.84</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>57.72</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>173.16</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>38.48</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Shares used (fraction of each country's total)</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Shares used (fraction of each country's total)</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Natural Rubber Gloves</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Nitrile Gloves</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Vinyl Gloves</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Neoprene Gloves</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Polyethylene Gloves</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Others</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Nitrile</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Latex</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Vinyl</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Neoprene</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Polyethylene</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Other Materials</t>
-        </is>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>China</t>
         </is>
       </c>
       <c r="B27" s="10" t="n">
-        <v>0.55</v>
+        <v>0.28</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>0.22</v>
+        <v>0.42</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="G27" s="10" t="n">
         <v>0.02</v>
@@ -2299,23 +2245,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B28" s="10" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C28" s="10" t="n">
         <v>0.42</v>
       </c>
-      <c r="C28" s="10" t="n">
-        <v>0.28</v>
-      </c>
       <c r="D28" s="10" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="G28" s="10" t="n">
         <v>0.02</v>
@@ -2324,14 +2270,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B29" s="10" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="C29" s="10" t="n">
-        <v>0.28</v>
+        <v>0.46</v>
       </c>
       <c r="D29" s="10" t="n">
         <v>0.12</v>
@@ -2340,7 +2286,7 @@
         <v>0.04</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="G29" s="10" t="n">
         <v>0.02</v>
@@ -2349,23 +2295,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>0.52</v>
+        <v>0.32</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>0.24</v>
+        <v>0.44</v>
       </c>
       <c r="D30" s="10" t="n">
         <v>0.12</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="G30" s="10" t="n">
         <v>0.02</v>
@@ -2374,23 +2320,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B31" s="10" t="n">
-        <v>0.5</v>
+        <v>0.28</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>0.26</v>
+        <v>0.48</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E31" s="10" t="n">
         <v>0.04</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="G31" s="10" t="n">
         <v>0.02</v>
@@ -2399,23 +2345,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B32" s="10" t="n">
-        <v>0.53</v>
+        <v>0.33</v>
       </c>
       <c r="C32" s="10" t="n">
-        <v>0.23</v>
+        <v>0.43</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>0.04</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="G32" s="10" t="n">
         <v>0.02</v>
@@ -2424,23 +2370,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B33" s="10" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="C33" s="10" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="G33" s="10" t="n">
         <v>0.02</v>
@@ -2449,23 +2395,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B34" s="10" t="n">
-        <v>0.44</v>
+        <v>0.3</v>
       </c>
       <c r="C34" s="10" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G34" s="10" t="n">
         <v>0.02</v>
@@ -2478,10 +2424,10 @@
         </is>
       </c>
       <c r="B35" s="10" t="n">
-        <v>0.54</v>
+        <v>0.26</v>
       </c>
       <c r="C35" s="10" t="n">
-        <v>0.23</v>
+        <v>0.5</v>
       </c>
       <c r="D35" s="10" t="n">
         <v>0.12</v>
@@ -2490,7 +2436,7 @@
         <v>0.04</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="G35" s="10" t="n">
         <v>0.02</v>
@@ -2499,23 +2445,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B36" s="10" t="n">
-        <v>0.49</v>
+        <v>0.28</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>0.27</v>
+        <v>0.48</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>0.04</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="G36" s="10" t="n">
         <v>0.02</v>
@@ -2524,23 +2470,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B37" s="10" t="n">
-        <v>0.51</v>
+        <v>0.3</v>
       </c>
       <c r="C37" s="10" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G37" s="10" t="n">
         <v>0.02</v>
@@ -2549,75 +2495,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Rest of World</t>
         </is>
       </c>
       <c r="B38" s="10" t="n">
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="C38" s="10" t="n">
-        <v>0.28</v>
+        <v>0.38</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>0.03</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="C39" s="10" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F39" s="10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G39" s="10" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Rest of World</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C40" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F40" s="10" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G40" s="10" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -2632,7 +2528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2644,7 +2540,7 @@
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>By Product Form -- TOP-DOWN (country total x share)</t>
+          <t>By Form -- TOP-DOWN (country total x share)</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2564,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Powder-Free</t>
+          <t>Non-powdered</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2684,13 +2580,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>460825.0085</v>
+        <v>3355.8593</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>4442141.1914</v>
+        <v>27986.7021</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>4902966.1999</v>
+        <v>31342.5614</v>
       </c>
     </row>
     <row r="5">
@@ -2700,13 +2596,13 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>29715.6236</v>
+        <v>85.1704</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>713174.9663</v>
+        <v>2044.0893</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>742890.5899</v>
+        <v>2129.2597</v>
       </c>
     </row>
     <row r="6">
@@ -2716,13 +2612,13 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>25739.6583</v>
+        <v>78.5424</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>617751.7992</v>
+        <v>1885.0173</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>643491.4575</v>
+        <v>1963.5597</v>
       </c>
     </row>
     <row r="7">
@@ -2732,13 +2628,13 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>3975.9653</v>
+        <v>6.628</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>95423.16710000001</v>
+        <v>159.072</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>99399.1324</v>
+        <v>165.7</v>
       </c>
     </row>
     <row r="8">
@@ -2748,13 +2644,13 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>25493.246</v>
+        <v>33.5994</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>186950.4707</v>
+        <v>369.6372</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>212443.7167</v>
+        <v>403.2366</v>
       </c>
     </row>
     <row r="9">
@@ -2764,13 +2660,13 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>7298.4856</v>
+        <v>21.5349</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>53522.2278</v>
+        <v>247.6517</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>60820.7134</v>
+        <v>269.1866</v>
       </c>
     </row>
     <row r="10">
@@ -2780,13 +2676,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>18194.7604</v>
+        <v>12.0645</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>133428.2429</v>
+        <v>121.9855</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>151623.0033</v>
+        <v>134.05</v>
       </c>
     </row>
     <row r="11">
@@ -2796,13 +2692,13 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>36641.2353</v>
+        <v>63.2095</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>743734.2442</v>
+        <v>1550.6925</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>780375.4795</v>
+        <v>1613.902</v>
       </c>
     </row>
     <row r="12">
@@ -2812,13 +2708,13 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>9510.1548</v>
+        <v>16.6578</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>228243.7147</v>
+        <v>538.6022</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>237753.8695</v>
+        <v>555.26</v>
       </c>
     </row>
     <row r="13">
@@ -2828,13 +2724,13 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>10144.2442</v>
+        <v>18.088</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>192740.6398</v>
+        <v>434.112</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>202884.884</v>
+        <v>452.2</v>
       </c>
     </row>
     <row r="14">
@@ -2844,13 +2740,13 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>8830.184499999999</v>
+        <v>7.4337</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>167773.5055</v>
+        <v>178.4083</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>176603.69</v>
+        <v>185.842</v>
       </c>
     </row>
     <row r="15">
@@ -2860,13 +2756,13 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8156.6518</v>
+        <v>21.03</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>154976.3842</v>
+        <v>399.57</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>163133.036</v>
+        <v>420.6</v>
       </c>
     </row>
     <row r="16">
@@ -2876,13 +2772,13 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>199531.6716</v>
+        <v>2981.48</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>1757415.9422</v>
+        <v>22290.6831</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1956947.6138</v>
+        <v>25272.1631</v>
       </c>
     </row>
     <row r="17">
@@ -2892,13 +2788,13 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>119346.3168</v>
+        <v>2768.3977</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>875206.3232</v>
+        <v>20301.583</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>994552.64</v>
+        <v>23069.9807</v>
       </c>
     </row>
     <row r="18">
@@ -2908,13 +2804,13 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>10556.2506</v>
+        <v>21.015</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>341318.7694</v>
+        <v>679.485</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>351875.02</v>
+        <v>700.5</v>
       </c>
     </row>
     <row r="19">
@@ -2924,13 +2820,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>61647.69</v>
+        <v>180</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>349336.91</v>
+        <v>1020</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>410984.6</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="20">
@@ -2940,117 +2836,114 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>4843.5051</v>
+        <v>12.0673</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>116244.122</v>
+        <v>289.6151</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>121087.6271</v>
+        <v>301.6824</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Australia</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n">
-        <v>3137.9091</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>75309.81759999999</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>78447.7267</v>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Rest of World</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>192.4</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>1731.6</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>1924</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Rest of World</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>169443.232</v>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>1040865.568</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>1210308.8</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t xml:space="preserve">   Rest of World</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n">
-        <v>169443.232</v>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>1040865.568</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>1210308.8</v>
+      <c r="B22" s="9" t="n">
+        <v>192.4</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>1731.6</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Shares used (fraction of each country's total)</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Shares used (fraction of each country's total)</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Powdered</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Non-powdered</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Powdered</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Powder-Free</t>
-        </is>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>0.96</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>China</t>
         </is>
       </c>
       <c r="B27" s="10" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>0.96</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B28" s="10" t="n">
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="C28" s="10" t="n">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B29" s="10" t="n">
@@ -3063,7 +2956,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B30" s="10" t="n">
@@ -3076,20 +2969,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B31" s="10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B32" s="10" t="n">
@@ -3102,27 +2995,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B33" s="10" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="C33" s="10" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B34" s="10" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="C34" s="10" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="35">
@@ -3141,66 +3034,40 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B36" s="10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B37" s="10" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="C37" s="10" t="n">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Rest of World</t>
         </is>
       </c>
       <c r="B38" s="10" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="C38" s="10" t="n">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C39" s="10" t="n">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Rest of World</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="C40" s="10" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
@@ -3214,1284 +3081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>By Sterility -- TOP-DOWN (country total x share)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Evidence status: web_evidence_backed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Geography</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Sterile</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Non-Sterile</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>1382804.0417</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>3520162.1582</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>4902966.1999</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>237724.9888</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>505165.6011</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>742890.5899</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   United States</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>205917.2664</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>437574.1911</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>643491.4575</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Canada</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>31807.7224</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>67591.41</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>99399.1324</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Latin America</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
-        <v>55843.5735</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>156600.1432</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>212443.7167</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Brazil</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>16421.5926</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>44399.1208</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>60820.7134</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Mexico</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>39421.9809</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>112201.0224</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>151623.0033</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>256369.3731</v>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>524006.1064</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>780375.4795</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Germany</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n">
-        <v>80836.3156</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>156917.5539</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>237753.8695</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   France</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>66952.0117</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>135932.8723</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>202884.884</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   United Kingdom</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n">
-        <v>54747.1439</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>121856.5461</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>176603.69</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Italy</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n">
-        <v>53833.9019</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>109299.1341</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>163133.036</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Asia Pacific</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>506082.7303</v>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>1450864.8835</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>1956947.6138</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   China</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n">
-        <v>218801.5808</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>775751.0592</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>994552.64</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Japan</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>123156.257</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>228718.763</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>351875.02</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   India</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="n">
-        <v>98636.304</v>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>312348.296</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>410984.6</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   South Korea</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n">
-        <v>41169.7932</v>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>79917.8339</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>121087.6271</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Australia</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n">
-        <v>24318.7953</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>54128.9314</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>78447.7267</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Rest of World</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>326783.376</v>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>883525.424</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>1210308.8</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Rest of World</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n">
-        <v>326783.376</v>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>883525.424</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>1210308.8</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Shares used (fraction of each country's total)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Sterile</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Non-Sterile</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="C27" s="10" t="n">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="C28" s="10" t="n">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C29" s="10" t="n">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="C30" s="10" t="n">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="C31" s="10" t="n">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="C32" s="10" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="C33" s="10" t="n">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="C34" s="10" t="n">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="C35" s="10" t="n">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="C36" s="10" t="n">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="C37" s="10" t="n">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="C38" s="10" t="n">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="C39" s="10" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Rest of World</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="C40" s="10" t="n">
-        <v>0.73</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>By Distribution Channel -- TOP-DOWN (country total x share)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Evidence status: web_evidence_backed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Geography</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Direct Sales to Healthcare Providers</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Distributors and Wholesalers</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Online and Retail Pharmacies</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>1176196.484</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>2800914.7565</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>925854.9594000001</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>4902966.1999</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>North America</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>257029.7325</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>374427.269</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>111433.5884</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>742890.5899</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   United States</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>225222.0101</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>321745.7288</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>96523.71859999999</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>643491.4575</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Canada</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>31807.7224</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>52681.5402</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>14909.8698</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>99399.1324</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Latin America</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
-        <v>42488.7434</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>127466.23</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>42488.7433</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>212443.7167</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Brazil</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>12164.1427</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>36492.428</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>12164.1427</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>60820.7134</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Mexico</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>30324.6007</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>90973.802</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>30324.6006</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>151623.0033</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>211056.6705</v>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>413243.7131</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>156075.0959</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>780375.4795</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Germany</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n">
-        <v>66571.08349999999</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>123632.0121</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>47550.7739</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>237753.8695</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   France</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>50721.221</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>111586.6862</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>40576.9768</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>202884.884</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   United Kingdom</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n">
-        <v>52981.107</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>88301.845</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>35320.738</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>176603.69</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Italy</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n">
-        <v>40783.259</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>89723.1698</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>32626.6072</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>163133.036</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Asia Pacific</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>423559.5776</v>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>1159592.2644</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>373795.7718</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>1956947.6138</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   China</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n">
-        <v>198910.528</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>596731.584</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>198910.528</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>994552.64</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Japan</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>105562.506</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>193531.261</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>52781.253</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>351875.02</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   India</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="n">
-        <v>61647.69</v>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>267139.99</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>82196.92</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>410984.6</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   South Korea</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n">
-        <v>33904.5356</v>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>62965.5661</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>24217.5254</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>121087.6271</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Australia</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n">
-        <v>23534.318</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>39223.8633</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>15689.5454</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>78447.7267</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Rest of World</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>242061.76</v>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>726185.28</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>242061.76</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>1210308.8</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Rest of World</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n">
-        <v>242061.76</v>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>726185.28</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>242061.76</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>1210308.8</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Shares used (fraction of each country's total)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Direct Sales to Healthcare Providers</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Distributors and Wholesalers</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Online and Retail Pharmacies</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C27" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D27" s="10" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C28" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D28" s="10" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C29" s="10" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="C30" s="10" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C31" s="10" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C32" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C33" s="10" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C34" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D34" s="10" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="C35" s="10" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D35" s="10" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C36" s="10" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D36" s="10" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="C37" s="10" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C38" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C39" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Rest of World</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C40" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4575,7 +3165,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>By Material</t>
+          <t>By Type</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -4585,7 +3175,7 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>llm_proposed</t>
+          <t>cmi_report_db</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
@@ -4595,19 +3185,19 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Nitrile gloves accounted for approximately 51.4% of the Medical Gloves Market in 2025, driven by allergy-free performance and chemical resistance. | The nitrile gloves segment dominated the medical gloves market with a market share of 42.8% and a value of USD 3.84 billion. | The natural rubber material segment dominated the market in 2023 with a share of 37.2% of the overall revenue. | Neoprene gloves represent the fastest-growing material segment, forecast to register a CAGR of 13.1% through 2035.</t>
+          <t>By material: Natural rubber segment held the largest market share of 36.1% in 2025. | By material, the natural rubber segment accounted for a share of 36.07% in 2025, owing to its superior elasticity and excellent tactile sensitivity for routine medical applications. | In terms of type, the natural rubber gloves segment is expected to command the share of 45.7% of the global disposable medical gloves market in 2026, due to their superior comfort, elasticity, and tactile sensitivity, which are essential for precision in surgical and diagnostic procedures. | Inspire Large Black Nitrile Gloves Disposable Latex Free, Exam Grade Medical Gloves, Food Service, Cleaning Gloves, Tattoo Supplies, case of 1000 ct.</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Global anchors from snippets: nitrile ~51.4% of medical gloves in 2025 (one source) and ~42.8% (another, likely narrower definition), latex/natural rubber ~37.2% in 2023 but declining as nitrile substitution continues. I set a global blended nitrile share near 50% and latex near 25%, with vinyl ~13-14%, neoprene ~4%, polyethylene ~4-5%, and other ~2%. Country variation reflects known adoption patterns: highest nitrile in US, Canada, UK, Germany, Australia, South Korea (strong allergy awareness, powder-free protocols, advanced healthcare); lower nitrile and higher latex/vinyl in India, China, Brazil, Mexico, Rest of World due to cost sensitivity and local latex production. Vinyl is elevated in price-sensitive and emerging markets; polyethylene is slightly higher in food-service-heavy and emerging markets. Neoprene remains small everywhere but fastest-growing. Figures are analyst estimates where snippets did not give country-level splits.</t>
+          <t>Snippets give global material shares: natural rubber ~36% (2025) and a type-level forecast of 45.7% for natural rubber in 2026, with nitrile widely understood to be the largest or co-largest material globally. I anchored global natural rubber near 30-36% and allocated the remainder primarily to nitrile, with vinyl and polyethylene as smaller commodity segments. Country differences reflect known regional preferences: US/Canada/Western Europe and South Korea skew heavily to nitrile due to latex allergy concerns and regulatory pressure; Japan and Southern Europe retain relatively higher natural rubber use for tactile-sensitive surgical/diagnostic work; China, India, Brazil, and Mexico have more price-sensitive markets with larger vinyl and polyethylene shares; India also has strong domestic natural rubber availability. Neoprene and other specialty materials are small everywhere. Where snippets lacked country-level figures, I used best industry knowledge and kept shares internally consistent so each country's fractions sum to 1.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>By Product Form</t>
+          <t>By Form</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -4617,7 +3207,7 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>llm_proposed</t>
+          <t>cmi_report_db</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -4627,112 +3217,84 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Powdered Disposable Gloves Market valued at $1.95 billion in 2025, projected to reach $2.58 billion by 2034, growing at 3.2% CAGR through advanced material innovations. | The global disposable medical gloves market size was USD 10.48 Billion in 2025 and is expected to register a revenue CAGR of 8.5% during the forecast period.</t>
+          <t>Powdered Disposable Gloves Market recorded a value of USD 349.76 Million in 2024 and is likely to attain USD 838.54 Million by 2032, increasing at a CAGR of 11.55% (2025-2032). | The global disposable medical gloves market size was USD 10.48 Billion in 2025 and is expected to register a revenue CAGR of 8.5% during the forecast period. | The nitrile segment accounted for a market share of 51.6% in 2025 due to its resistance to chemicals, punctures, and tears, along with its latex-free composition suitable for users with latex sensitivity.</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>No snippet gives a direct powdered vs powder-free split by country. The only quantified anchor is the global powdered disposable gloves market at $1.95B in 2025 versus a global disposable medical gloves market of $10.48B in 2025, implying roughly 18-19% powdered globally. However, that powdered figure likely spans non-medical/industrial use too, and clinical guidelines in developed markets have largely eliminated powdered surgical/exam gloves, so I applied lower powdered shares in high-income, tightly regulated markets (US, Japan, Germany, France, UK, Canada, Italy, South Korea, Australia: 3-5%) and higher shares in emerging markets where powdered latex exam gloves remain common for cost and donning ease (India 15%, China/Brazil/Mexico 12%, Rest of World 14%). These are analyst estimates based on industry knowledge, not snippet-derived country data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>By Sterility</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>top_down</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>llm_proposed</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>web_evidence_backed</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>Sterile gloves dominated with 68.0% revenue share | Sterile gloves dominated with 68.0% revenue share | Sterile medical gloves market valued at $7.34 billion in 2025, projected to reach $13.73 billion by 2034, growing at 6.8% CAGR. | Disposable Medical Sterile Surgical Gloves Market forecasted to expand from 4.25 billion USD in 2024 to 7.50 billion USD by 2033, achieving a CAGR of 6.5%</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>The snippets give a global sterility split only for the narrower disposable surgical gloves market (sterile 68%), while the broader disposable medical gloves market is dominated by non-sterile examination gloves. I therefore set non-sterile shares well above sterile for all countries, using the surgical-glove 68% sterile figure as an upper anchor for sterile-intensive settings and adjusting downward for the full disposable medical gloves market. Country differences reflect healthcare development, surgical volume, and infection-control maturity: mature Western markets (US, Japan, Germany, France, Italy, Canada, South Korea, Australia, UK) have higher sterile shares (~31-35%) due to surgical and cleanroom demand, while emerging markets (China, India, Mexico, Brazil, Rest of World) skew more to non-sterile examination gloves (~22-27% sterile). No country-level sterility figures were provided in the snippets, so these are best-estimate allocations consistent with the cited global anchors.</t>
+          <t>The snippets provide a global powdered disposable gloves value (USD 349.76M in 2024) and a global disposable medical gloves market size (USD 10.48B in 2025), implying a global powdered share of roughly 3-4%. However, the powdered figure is for the broader disposable gloves market, not strictly medical, and powdered medical gloves are largely banned or phased out in the US, Canada, and EU. I therefore set very low powdered shares (3-5%) for developed Western markets and Japan/South Korea, moderately higher shares for China, Brazil, Mexico, and Rest of World (8-12%) where regulatory restrictions are less strict and cost sensitivity is higher, and the highest share for India (15%) given its large price-sensitive healthcare sector and less stringent enforcement. Non-powdered shares are the complements. These country-level splits are based on industry knowledge and regulatory context rather than direct country-level figures in the snippets.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>By Distribution Channel</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>top_down</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>llm_proposed</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>web_evidence_backed</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>Supermarkets and hypermarkets serve household consumers and small food operations with 19.4% share, while industrial and direct channels contribute 11.5% to overall distribution.</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>The snippets provide no country-level distribution channel splits for disposable medical gloves, so shares are estimated using industry knowledge. Distributors and wholesalers dominate most markets because gloves are low-value, high-volume consumables routed through healthcare GPOs, hospital group purchasing, and national wholesalers. Direct sales are higher in the US, Canada, Japan, and Western Europe where large hospital systems and integrated providers buy directly or through GPO contracts. Online and retail pharmacy shares are modest but growing, supported by the snippet noting e-commerce as a distribution channel; they are slightly higher in markets with strong retail pharmacy and e-commerce penetration (US, Germany, UK, South Korea) and lower where institutional procurement dominates. China, India, Brazil, Mexico, and Rest of World rely more heavily on multi-tier distributor networks, so distributor shares are set higher. All rows sum to 1.</t>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Consistency checks (every dimension must add back to the same country and global totals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Dimension</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Max country gap (USD Mn)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Global gap (USD Mn)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Consistency checks (every dimension must add back to the same country and global totals)</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>By Application (bottom-up)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Dimension</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Max country gap (USD Mn)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Global gap (USD Mn)</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Passed</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>By Type</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>By Application (bottom-up)</t>
+          <t>By Form</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -4742,78 +3304,6 @@
         <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>By Material</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>By Product Form</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>By Sterility</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>By Distribution Channel</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
